--- a/backend/exports/session_10_autoexport.xlsx
+++ b/backend/exports/session_10_autoexport.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -589,6 +589,41 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>23153000034</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Arti</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>14:08:32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
